--- a/Name.xlsx
+++ b/Name.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ztemp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\我的資料_路亞國際學校\02A.電腦課程\題庫系統\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77D36CCF-BCEC-4116-AFED-12FAB2E8A4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE22942B-0E8E-4D64-859C-ED2A8AE967C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7DCBFBB1-30D6-49BD-98B1-80C988443001}"/>
   </bookViews>
@@ -98,151 +98,154 @@
     <t>Nick Huang</t>
   </si>
   <si>
+    <t>Matteo Cheng</t>
+  </si>
+  <si>
+    <t>Auston Lai</t>
+  </si>
+  <si>
+    <t>Ansel Lai</t>
+  </si>
+  <si>
+    <t>Zack Lin</t>
+  </si>
+  <si>
+    <t>Kane Lee</t>
+  </si>
+  <si>
+    <t>Rachel Sun</t>
+  </si>
+  <si>
+    <t>Sydney Lee</t>
+  </si>
+  <si>
+    <t>Emily Lin</t>
+  </si>
+  <si>
+    <t>Ray Yeh</t>
+  </si>
+  <si>
+    <t>Joshua Hsieh</t>
+  </si>
+  <si>
+    <t>Aria Loh</t>
+  </si>
+  <si>
+    <t>Jasmine Pei</t>
+  </si>
+  <si>
+    <t>Jason Tsai</t>
+  </si>
+  <si>
+    <t>Janice Liang</t>
+  </si>
+  <si>
+    <t>Naomi Chang</t>
+  </si>
+  <si>
+    <t>Chloe Chang</t>
+  </si>
+  <si>
+    <t>Kyle Chang</t>
+  </si>
+  <si>
+    <t>Rapunzel Fu</t>
+  </si>
+  <si>
+    <t>Amanda Lin</t>
+  </si>
+  <si>
+    <t>Timmy Chen</t>
+  </si>
+  <si>
+    <t>Mia Chen</t>
+  </si>
+  <si>
+    <t>Harvey Chen</t>
+  </si>
+  <si>
+    <t>Roy Chou</t>
+  </si>
+  <si>
+    <t>Jill Liao</t>
+  </si>
+  <si>
+    <t>Wayne Hsieh</t>
+  </si>
+  <si>
+    <t>Shannon Liu</t>
+  </si>
+  <si>
+    <t>Ray Lin</t>
+  </si>
+  <si>
+    <t>Grace Yeh</t>
+  </si>
+  <si>
+    <t>Nathan Lin</t>
+  </si>
+  <si>
+    <t>Andrew Yeh</t>
+  </si>
+  <si>
+    <t>Andely Hsieh</t>
+  </si>
+  <si>
+    <t>Angelina Hsieh</t>
+  </si>
+  <si>
+    <t>Nini Huang</t>
+  </si>
+  <si>
+    <t>Gabriel Chen</t>
+  </si>
+  <si>
+    <t>Rick Wei</t>
+  </si>
+  <si>
+    <t>Elly Lin</t>
+  </si>
+  <si>
+    <t>Alice Yuan</t>
+  </si>
+  <si>
+    <t>Baron Yao</t>
+  </si>
+  <si>
+    <t>Dean Huang</t>
+  </si>
+  <si>
+    <t>Erica Wu</t>
+  </si>
+  <si>
+    <t>Brian Chen</t>
+  </si>
+  <si>
+    <t>Eason Chen</t>
+  </si>
+  <si>
+    <t>Yulin Huang</t>
+  </si>
+  <si>
+    <t>Jason Hsu</t>
+  </si>
+  <si>
+    <t>Diana Teng</t>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yosi Chiang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Josh Chen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Joe Lin</t>
-  </si>
-  <si>
-    <t>Matteo Cheng</t>
-  </si>
-  <si>
-    <t>Auston Lai</t>
-  </si>
-  <si>
-    <t>Ansel Lai</t>
-  </si>
-  <si>
-    <t>Zack Lin</t>
-  </si>
-  <si>
-    <t>Kane Lee</t>
-  </si>
-  <si>
-    <t>Rachel Sun</t>
-  </si>
-  <si>
-    <t>Sydney Lee</t>
-  </si>
-  <si>
-    <t>Emily Lin</t>
-  </si>
-  <si>
-    <t>Ray Yeh</t>
-  </si>
-  <si>
-    <t>Joshua Hsieh</t>
-  </si>
-  <si>
-    <t>Aria Loh</t>
-  </si>
-  <si>
-    <t>Jasmine Pei</t>
-  </si>
-  <si>
-    <t>Josh Chen</t>
-  </si>
-  <si>
-    <t>Yosi  Chiang</t>
-  </si>
-  <si>
-    <t>Jason Tsai</t>
-  </si>
-  <si>
-    <t>Janice Liang</t>
-  </si>
-  <si>
-    <t>Naomi Chang</t>
-  </si>
-  <si>
-    <t>Chloe Chang</t>
-  </si>
-  <si>
-    <t>Kyle Chang</t>
-  </si>
-  <si>
-    <t>Rapunzel Fu</t>
-  </si>
-  <si>
-    <t>Amanda Lin</t>
-  </si>
-  <si>
-    <t>Timmy Chen</t>
-  </si>
-  <si>
-    <t>Mia Chen</t>
-  </si>
-  <si>
-    <t>Harvey Chen</t>
-  </si>
-  <si>
-    <t>Roy Chou</t>
-  </si>
-  <si>
-    <t>Jill Liao</t>
-  </si>
-  <si>
-    <t>Wayne Hsieh</t>
-  </si>
-  <si>
-    <t>Shannon Liu</t>
-  </si>
-  <si>
-    <t>Ray Lin</t>
-  </si>
-  <si>
-    <t>Grace Yeh</t>
-  </si>
-  <si>
-    <t>Nathan Lin</t>
-  </si>
-  <si>
-    <t>Andrew Yeh</t>
-  </si>
-  <si>
-    <t>Andely Hsieh</t>
-  </si>
-  <si>
-    <t>Angelina Hsieh</t>
-  </si>
-  <si>
-    <t>Nini Huang</t>
-  </si>
-  <si>
-    <t>Gabriel Chen</t>
-  </si>
-  <si>
-    <t>Rick Wei</t>
-  </si>
-  <si>
-    <t>Elly Lin</t>
-  </si>
-  <si>
-    <t>Alice Yuan</t>
-  </si>
-  <si>
-    <t>Baron Yao</t>
-  </si>
-  <si>
-    <t>Dean Huang</t>
-  </si>
-  <si>
-    <t>Erica Wu</t>
-  </si>
-  <si>
-    <t>Brian Chen</t>
-  </si>
-  <si>
-    <t>Eason Chen</t>
-  </si>
-  <si>
-    <t>Yulin Huang</t>
-  </si>
-  <si>
-    <t>Jason Hsu</t>
-  </si>
-  <si>
-    <t>Diana Teng</t>
-  </si>
-  <si>
-    <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -635,172 +638,172 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
@@ -905,77 +908,77 @@
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Name.xlsx
+++ b/Name.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\我的資料_路亞國際學校\02A.電腦課程\題庫系統\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE22942B-0E8E-4D64-859C-ED2A8AE967C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5B63B7-F88D-4D9F-AC7B-7F9FF8D814A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7DCBFBB1-30D6-49BD-98B1-80C988443001}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7DCBFBB1-30D6-49BD-98B1-80C988443001}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="74">
   <si>
     <t>Jayden Lee</t>
   </si>
@@ -246,6 +246,26 @@
   </si>
   <si>
     <t>Joe Lin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -292,9 +312,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,354 +656,562 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{623AE36C-F2A7-441C-93D3-E708820A8AF6}">
-  <dimension ref="A1:A69"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B34" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B35" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B39" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B41" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B45" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B46" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B48" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B50" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B51" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B52" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B53" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B54" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B55" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B56" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B57" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B58" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B59" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B60" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B61" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B62" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B63" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B68" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" t="s">
         <v>66</v>
       </c>
     </row>
